--- a/backend/Plantillas/autorizacion_contr.xlsx
+++ b/backend/Plantillas/autorizacion_contr.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a9c14fa8f1561f77/Desktop/sistema_contratos/Plantillas/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sistema-charaña\backend\Plantillas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{A7DF31D7-E029-4315-B292-2871E7AB3426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0830D9D8-6393-4ACA-8A8D-1E10AEC4B455}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B04188E-E416-4274-884A-3A1B94A8AD80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{69706378-BA01-4536-A2F5-9D3D18ED615D}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="41">
   <si>
     <t>N.I.T:</t>
   </si>
@@ -119,9 +119,6 @@
   </si>
   <si>
     <t>{OBJETO}</t>
-  </si>
-  <si>
-    <t>{DESCRIPCION}</t>
   </si>
   <si>
     <t>{TIPUNI}</t>
@@ -671,6 +668,83 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="1"/>
     </xf>
@@ -720,83 +794,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1291,112 +1288,112 @@
     </row>
     <row r="2" spans="2:10">
       <c r="B2" s="4"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="29"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="56"/>
     </row>
     <row r="3" spans="2:10">
       <c r="B3" s="4"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
-      <c r="G3" s="29"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="56"/>
       <c r="J3" s="10"/>
     </row>
     <row r="4" spans="2:10">
       <c r="B4" s="4"/>
-      <c r="C4" s="30"/>
-      <c r="D4" s="32"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="33"/>
-      <c r="G4" s="34"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="61"/>
     </row>
     <row r="5" spans="2:10" ht="15.75" thickBot="1">
       <c r="B5" s="5"/>
-      <c r="C5" s="31"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="36"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="62"/>
+      <c r="E5" s="62"/>
+      <c r="F5" s="62"/>
+      <c r="G5" s="63"/>
     </row>
     <row r="6" spans="2:10" ht="16.5" thickTop="1" thickBot="1">
       <c r="B6" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C6" s="37">
+      <c r="C6" s="64">
         <v>125545029</v>
       </c>
-      <c r="D6" s="37"/>
+      <c r="D6" s="64"/>
       <c r="E6" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="F6" s="38" t="s">
+      <c r="F6" s="65" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="38"/>
+      <c r="G6" s="65"/>
     </row>
     <row r="7" spans="2:10" ht="25.5" thickTop="1" thickBot="1">
       <c r="B7" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="39" t="s">
-        <v>40</v>
-      </c>
-      <c r="D7" s="40"/>
-      <c r="E7" s="40"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="41"/>
+      <c r="C7" s="66" t="s">
+        <v>39</v>
+      </c>
+      <c r="D7" s="67"/>
+      <c r="E7" s="67"/>
+      <c r="F7" s="67"/>
+      <c r="G7" s="68"/>
     </row>
     <row r="8" spans="2:10" ht="16.5" thickTop="1" thickBot="1">
       <c r="B8" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="39" t="s">
+      <c r="C8" s="66" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="40"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="40"/>
-      <c r="G8" s="41"/>
+      <c r="D8" s="67"/>
+      <c r="E8" s="67"/>
+      <c r="F8" s="67"/>
+      <c r="G8" s="68"/>
     </row>
     <row r="9" spans="2:10" ht="25.5" thickTop="1" thickBot="1">
       <c r="B9" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="25" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="26"/>
-      <c r="E9" s="26"/>
-      <c r="F9" s="26"/>
-      <c r="G9" s="27"/>
+      <c r="C9" s="52" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="53"/>
+      <c r="E9" s="53"/>
+      <c r="F9" s="53"/>
+      <c r="G9" s="54"/>
     </row>
     <row r="10" spans="2:10" ht="16.5" thickTop="1" thickBot="1">
       <c r="B10" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="42" t="s">
+      <c r="C10" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="43"/>
-      <c r="E10" s="43"/>
-      <c r="F10" s="43"/>
-      <c r="G10" s="44"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="41"/>
     </row>
     <row r="11" spans="2:10" ht="25.5" thickTop="1" thickBot="1">
       <c r="B11" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="45" t="s">
+      <c r="C11" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="46"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="46"/>
-      <c r="G11" s="47"/>
+      <c r="D11" s="43"/>
+      <c r="E11" s="43"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="44"/>
     </row>
     <row r="12" spans="2:10" ht="16.5" thickTop="1" thickBot="1">
       <c r="B12" s="8" t="s">
@@ -1407,68 +1404,66 @@
         <v>10</v>
       </c>
       <c r="E12" s="8"/>
-      <c r="F12" s="48" t="str">
+      <c r="F12" s="45" t="str">
         <f>G35</f>
         <v>{TOTAL}</v>
       </c>
-      <c r="G12" s="49"/>
+      <c r="G12" s="46"/>
     </row>
     <row r="13" spans="2:10" ht="16.5" thickTop="1" thickBot="1">
-      <c r="B13" s="57" t="s">
+      <c r="B13" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="58" t="s">
+      <c r="C13" s="25" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="59" t="s">
+      <c r="D13" s="49" t="s">
         <v>13</v>
       </c>
-      <c r="E13" s="60" t="s">
+      <c r="E13" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="F13" s="59" t="s">
+      <c r="F13" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="G13" s="59" t="s">
+      <c r="G13" s="49" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="14" spans="2:10" ht="35.25" customHeight="1" thickTop="1" thickBot="1">
-      <c r="B14" s="61"/>
-      <c r="C14" s="62" t="s">
+      <c r="B14" s="48"/>
+      <c r="C14" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="D14" s="59"/>
-      <c r="E14" s="63"/>
-      <c r="F14" s="59"/>
-      <c r="G14" s="59"/>
+      <c r="D14" s="49"/>
+      <c r="E14" s="51"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="49"/>
     </row>
     <row r="15" spans="2:10" ht="11.25" customHeight="1" thickTop="1">
       <c r="B15" s="17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C15" s="23" t="s">
         <v>29</v>
       </c>
       <c r="D15" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="E15" s="21" t="s">
+      <c r="F15" s="19" t="s">
         <v>32</v>
-      </c>
-      <c r="F15" s="19" t="s">
-        <v>33</v>
       </c>
       <c r="G15" s="20" t="e">
         <f>F15*E15</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="16" spans="2:10" ht="15" customHeight="1">
+    <row r="16" spans="2:10">
       <c r="B16" s="15"/>
-      <c r="C16" s="11" t="s">
-        <v>30</v>
-      </c>
+      <c r="C16" s="11"/>
       <c r="D16" s="16"/>
       <c r="E16" s="22"/>
       <c r="F16" s="12"/>
@@ -1676,15 +1671,15 @@
       </c>
     </row>
     <row r="35" spans="2:7" ht="15.75" thickBot="1">
-      <c r="B35" s="64" t="s">
+      <c r="B35" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="C35" s="64"/>
-      <c r="D35" s="64"/>
-      <c r="E35" s="64"/>
-      <c r="F35" s="64"/>
-      <c r="G35" s="65" t="s">
-        <v>39</v>
+      <c r="C35" s="34"/>
+      <c r="D35" s="34"/>
+      <c r="E35" s="34"/>
+      <c r="F35" s="34"/>
+      <c r="G35" s="27" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="36" spans="2:7" ht="16.5" thickTop="1" thickBot="1">
@@ -1692,12 +1687,12 @@
         <v>19</v>
       </c>
       <c r="C36" s="9"/>
-      <c r="D36" s="54" t="s">
-        <v>36</v>
-      </c>
-      <c r="E36" s="54"/>
-      <c r="F36" s="54"/>
-      <c r="G36" s="54"/>
+      <c r="D36" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="E36" s="35"/>
+      <c r="F36" s="35"/>
+      <c r="G36" s="35"/>
     </row>
     <row r="37" spans="2:7" ht="16.5" thickTop="1" thickBot="1">
       <c r="B37" s="14" t="s">
@@ -1706,140 +1701,156 @@
       <c r="C37" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D37" s="54"/>
-      <c r="E37" s="54"/>
-      <c r="F37" s="54"/>
-      <c r="G37" s="54"/>
+      <c r="D37" s="35"/>
+      <c r="E37" s="35"/>
+      <c r="F37" s="35"/>
+      <c r="G37" s="35"/>
     </row>
     <row r="38" spans="2:7" ht="16.5" thickTop="1" thickBot="1">
       <c r="B38" s="9"/>
       <c r="C38" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D38" s="54"/>
-      <c r="E38" s="54"/>
-      <c r="F38" s="54"/>
-      <c r="G38" s="54"/>
+      <c r="D38" s="35"/>
+      <c r="E38" s="35"/>
+      <c r="F38" s="35"/>
+      <c r="G38" s="35"/>
     </row>
     <row r="39" spans="2:7" ht="16.5" thickTop="1" thickBot="1">
-      <c r="B39" s="66" t="s">
+      <c r="B39" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="C39" s="66"/>
-      <c r="D39" s="66"/>
-      <c r="E39" s="66"/>
-      <c r="F39" s="66"/>
-      <c r="G39" s="66"/>
+      <c r="C39" s="36"/>
+      <c r="D39" s="36"/>
+      <c r="E39" s="36"/>
+      <c r="F39" s="36"/>
+      <c r="G39" s="36"/>
     </row>
     <row r="40" spans="2:7" ht="16.5" thickTop="1" thickBot="1">
-      <c r="B40" s="67" t="s">
+      <c r="B40" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="C40" s="55" t="s">
-        <v>41</v>
-      </c>
-      <c r="D40" s="55"/>
-      <c r="E40" s="55"/>
-      <c r="F40" s="55"/>
-      <c r="G40" s="55"/>
+      <c r="C40" s="37" t="s">
+        <v>40</v>
+      </c>
+      <c r="D40" s="37"/>
+      <c r="E40" s="37"/>
+      <c r="F40" s="37"/>
+      <c r="G40" s="37"/>
     </row>
     <row r="41" spans="2:7" ht="16.5" thickTop="1" thickBot="1">
-      <c r="B41" s="67" t="s">
+      <c r="B41" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="C41" s="56" t="s">
+      <c r="C41" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="D41" s="38"/>
+      <c r="E41" s="38"/>
+      <c r="F41" s="38"/>
+      <c r="G41" s="38"/>
+    </row>
+    <row r="42" spans="2:7" ht="16.5" thickTop="1" thickBot="1">
+      <c r="B42" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="C42" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="D41" s="56"/>
-      <c r="E41" s="56"/>
-      <c r="F41" s="56"/>
-      <c r="G41" s="56"/>
-    </row>
-    <row r="42" spans="2:7" ht="16.5" thickTop="1" thickBot="1">
-      <c r="B42" s="67" t="s">
-        <v>20</v>
-      </c>
-      <c r="C42" s="56" t="s">
-        <v>38</v>
-      </c>
-      <c r="D42" s="56"/>
-      <c r="E42" s="56"/>
-      <c r="F42" s="56"/>
-      <c r="G42" s="56"/>
+      <c r="D42" s="38"/>
+      <c r="E42" s="38"/>
+      <c r="F42" s="38"/>
+      <c r="G42" s="38"/>
     </row>
     <row r="43" spans="2:7" ht="16.5" thickTop="1" thickBot="1">
-      <c r="B43" s="67"/>
-      <c r="C43" s="50" t="s">
+      <c r="B43" s="28"/>
+      <c r="C43" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="D43" s="50"/>
-      <c r="E43" s="50"/>
-      <c r="F43" s="50"/>
-      <c r="G43" s="50"/>
+      <c r="D43" s="29"/>
+      <c r="E43" s="29"/>
+      <c r="F43" s="29"/>
+      <c r="G43" s="29"/>
     </row>
     <row r="44" spans="2:7" ht="16.5" thickTop="1" thickBot="1">
-      <c r="B44" s="68" t="s">
+      <c r="B44" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="C44" s="68"/>
-      <c r="D44" s="68"/>
-      <c r="E44" s="68"/>
-      <c r="F44" s="68"/>
-      <c r="G44" s="68"/>
+      <c r="C44" s="30"/>
+      <c r="D44" s="30"/>
+      <c r="E44" s="30"/>
+      <c r="F44" s="30"/>
+      <c r="G44" s="30"/>
     </row>
     <row r="45" spans="2:7" ht="16.5" thickTop="1" thickBot="1">
-      <c r="B45" s="51"/>
-      <c r="C45" s="51"/>
-      <c r="D45" s="51"/>
-      <c r="E45" s="51"/>
-      <c r="F45" s="51"/>
-      <c r="G45" s="51"/>
+      <c r="B45" s="31"/>
+      <c r="C45" s="31"/>
+      <c r="D45" s="31"/>
+      <c r="E45" s="31"/>
+      <c r="F45" s="31"/>
+      <c r="G45" s="31"/>
     </row>
     <row r="46" spans="2:7" ht="16.5" thickTop="1" thickBot="1">
-      <c r="B46" s="51"/>
-      <c r="C46" s="51"/>
-      <c r="D46" s="51"/>
-      <c r="E46" s="51"/>
-      <c r="F46" s="51"/>
-      <c r="G46" s="51"/>
+      <c r="B46" s="31"/>
+      <c r="C46" s="31"/>
+      <c r="D46" s="31"/>
+      <c r="E46" s="31"/>
+      <c r="F46" s="31"/>
+      <c r="G46" s="31"/>
     </row>
     <row r="47" spans="2:7" ht="16.5" thickTop="1" thickBot="1">
-      <c r="B47" s="51"/>
-      <c r="C47" s="51"/>
-      <c r="D47" s="51"/>
-      <c r="E47" s="51"/>
-      <c r="F47" s="51"/>
-      <c r="G47" s="51"/>
+      <c r="B47" s="31"/>
+      <c r="C47" s="31"/>
+      <c r="D47" s="31"/>
+      <c r="E47" s="31"/>
+      <c r="F47" s="31"/>
+      <c r="G47" s="31"/>
     </row>
     <row r="48" spans="2:7" ht="16.5" thickTop="1" thickBot="1">
-      <c r="B48" s="51"/>
-      <c r="C48" s="51"/>
-      <c r="D48" s="51"/>
-      <c r="E48" s="51"/>
-      <c r="F48" s="51"/>
-      <c r="G48" s="51"/>
+      <c r="B48" s="31"/>
+      <c r="C48" s="31"/>
+      <c r="D48" s="31"/>
+      <c r="E48" s="31"/>
+      <c r="F48" s="31"/>
+      <c r="G48" s="31"/>
     </row>
     <row r="49" spans="2:7" ht="16.5" thickTop="1" thickBot="1">
-      <c r="B49" s="51"/>
-      <c r="C49" s="51"/>
-      <c r="D49" s="51"/>
-      <c r="E49" s="51"/>
-      <c r="F49" s="51"/>
-      <c r="G49" s="51"/>
+      <c r="B49" s="31"/>
+      <c r="C49" s="31"/>
+      <c r="D49" s="31"/>
+      <c r="E49" s="31"/>
+      <c r="F49" s="31"/>
+      <c r="G49" s="31"/>
     </row>
     <row r="50" spans="2:7" ht="16.5" thickTop="1" thickBot="1">
-      <c r="B50" s="52" t="s">
+      <c r="B50" s="32" t="s">
         <v>26</v>
       </c>
-      <c r="C50" s="53"/>
-      <c r="D50" s="53"/>
-      <c r="E50" s="53"/>
-      <c r="F50" s="53"/>
-      <c r="G50" s="53"/>
+      <c r="C50" s="33"/>
+      <c r="D50" s="33"/>
+      <c r="E50" s="33"/>
+      <c r="F50" s="33"/>
+      <c r="G50" s="33"/>
     </row>
     <row r="51" spans="2:7" ht="15.75" thickTop="1"/>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C2:G3"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:G5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E13:E14"/>
+    <mergeCell ref="F13:F14"/>
+    <mergeCell ref="G13:G14"/>
     <mergeCell ref="C43:G43"/>
     <mergeCell ref="B44:G44"/>
     <mergeCell ref="B45:G49"/>
@@ -1850,22 +1861,6 @@
     <mergeCell ref="C40:G40"/>
     <mergeCell ref="C41:G41"/>
     <mergeCell ref="C42:G42"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E13:E14"/>
-    <mergeCell ref="F13:F14"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C2:G3"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:G5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="C8:G8"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
